--- a/evals/fixtures/eval_data.xlsx
+++ b/evals/fixtures/eval_data.xlsx
@@ -530,17 +530,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Quantum Computing Specialist</t>
+          <t>COBOL Mainframe Engineer</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Quantum Computing (expert); Q# (expert)</t>
+          <t>COBOL (expert); JCL (expert)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
